--- a/01_project_planning/Voter Registration Table Schema.xlsx
+++ b/01_project_planning/Voter Registration Table Schema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Advanced Analytics\Ownership-Occupied-Prediction\01_project_planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BA562B-DD67-4EDB-839F-789D31893BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4405B0-9504-46A6-8868-4D074F57A2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{1DAAE89E-E9A4-41D8-B5F3-91124023B027}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{1DAAE89E-E9A4-41D8-B5F3-91124023B027}"/>
   </bookViews>
   <sheets>
     <sheet name="Schema" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>Voter ID</t>
   </si>
@@ -116,9 +116,6 @@
     <t>Indicator for whether the registration is active (A) or inactive (I)</t>
   </si>
   <si>
-    <t>Load Date</t>
-  </si>
-  <si>
     <t>MM/DD/YYYY</t>
   </si>
   <si>
@@ -128,10 +125,13 @@
     <t>Date of purchase from the Pennsylvania Department of State; MM/DD/YYYY</t>
   </si>
   <si>
-    <t>Property Owner ID</t>
-  </si>
-  <si>
     <t>Date Status Change</t>
+  </si>
+  <si>
+    <t>Property Owner Key</t>
+  </si>
+  <si>
+    <t>Purchase Date</t>
   </si>
 </sst>
 </file>
@@ -504,12 +504,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{116F94EE-80D7-4227-B230-E80220153AE8}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.54296875" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -517,7 +517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -525,136 +525,142 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
